--- a/Timesheet-Project/Timesheet 3/Charmane/Charmane_Mchunu_March_FinalWeek.xlsx
+++ b/Timesheet-Project/Timesheet 3/Charmane/Charmane_Mchunu_March_FinalWeek.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sc_LwazisileMhlambi_2026\Timesheet-Project\Timesheet 3\Charmane\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Charmaine Mchunu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDBDF0E4-0E3E-427D-AA2A-5B31600B960D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1812" yWindow="1812" windowWidth="17280" windowHeight="8880" firstSheet="5" activeTab="5" xr2:uid="{1C8F8026-B005-4B08-94D3-371A77F74D8F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="5" xr2:uid="{1C8F8026-B005-4B08-94D3-371A77F74D8F}"/>
   </bookViews>
   <sheets>
     <sheet name="Oct" sheetId="10" r:id="rId1"/>
@@ -1974,28 +1974,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2011,6 +1996,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -12623,118 +12623,118 @@
       <c r="F7" s="86"/>
     </row>
     <row r="8" spans="1:15" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="124" t="s">
+      <c r="A8" s="127" t="s">
         <v>66</v>
       </c>
-      <c r="B8" s="124"/>
-      <c r="C8" s="124"/>
-      <c r="D8" s="124"/>
-      <c r="E8" s="124"/>
-      <c r="F8" s="124"/>
+      <c r="B8" s="127"/>
+      <c r="C8" s="127"/>
+      <c r="D8" s="127"/>
+      <c r="E8" s="127"/>
+      <c r="F8" s="127"/>
     </row>
     <row r="9" spans="1:15" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="83" t="s">
         <v>67</v>
       </c>
-      <c r="B9" s="121" t="s">
+      <c r="B9" s="130" t="s">
         <v>68</v>
       </c>
-      <c r="C9" s="122"/>
-      <c r="D9" s="121" t="s">
+      <c r="C9" s="131"/>
+      <c r="D9" s="130" t="s">
         <v>69</v>
       </c>
-      <c r="E9" s="122"/>
+      <c r="E9" s="131"/>
       <c r="F9" s="84" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="79"/>
-      <c r="B10" s="123" t="s">
+      <c r="B10" s="121" t="s">
         <v>71</v>
       </c>
-      <c r="C10" s="123"/>
-      <c r="D10" s="123" t="s">
+      <c r="C10" s="121"/>
+      <c r="D10" s="121" t="s">
         <v>72</v>
       </c>
-      <c r="E10" s="123"/>
+      <c r="E10" s="121"/>
       <c r="F10" s="78">
         <v>200</v>
       </c>
-      <c r="G10" s="119" t="s">
+      <c r="G10" s="128" t="s">
         <v>73</v>
       </c>
-      <c r="H10" s="120"/>
-      <c r="I10" s="120"/>
-      <c r="J10" s="120"/>
-      <c r="K10" s="120"/>
-      <c r="L10" s="120"/>
-      <c r="M10" s="120"/>
-      <c r="N10" s="120"/>
-      <c r="O10" s="120"/>
+      <c r="H10" s="129"/>
+      <c r="I10" s="129"/>
+      <c r="J10" s="129"/>
+      <c r="K10" s="129"/>
+      <c r="L10" s="129"/>
+      <c r="M10" s="129"/>
+      <c r="N10" s="129"/>
+      <c r="O10" s="129"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="79"/>
-      <c r="B11" s="125" t="s">
+      <c r="B11" s="119" t="s">
         <v>74</v>
       </c>
-      <c r="C11" s="126"/>
-      <c r="D11" s="123" t="s">
+      <c r="C11" s="120"/>
+      <c r="D11" s="121" t="s">
         <v>75</v>
       </c>
-      <c r="E11" s="123"/>
+      <c r="E11" s="121"/>
       <c r="F11" s="78"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="79"/>
-      <c r="B12" s="125" t="s">
+      <c r="B12" s="119" t="s">
         <v>76</v>
       </c>
-      <c r="C12" s="126"/>
-      <c r="D12" s="123"/>
-      <c r="E12" s="123"/>
+      <c r="C12" s="120"/>
+      <c r="D12" s="121"/>
+      <c r="E12" s="121"/>
       <c r="F12" s="78"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="79"/>
-      <c r="B13" s="125"/>
-      <c r="C13" s="126"/>
-      <c r="D13" s="123"/>
-      <c r="E13" s="123"/>
+      <c r="B13" s="119"/>
+      <c r="C13" s="120"/>
+      <c r="D13" s="121"/>
+      <c r="E13" s="121"/>
       <c r="F13" s="78"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="79"/>
-      <c r="B14" s="125"/>
-      <c r="C14" s="126"/>
-      <c r="D14" s="123"/>
-      <c r="E14" s="123"/>
+      <c r="B14" s="119"/>
+      <c r="C14" s="120"/>
+      <c r="D14" s="121"/>
+      <c r="E14" s="121"/>
       <c r="F14" s="78"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="79"/>
-      <c r="B15" s="130"/>
-      <c r="C15" s="131"/>
-      <c r="D15" s="123"/>
-      <c r="E15" s="123"/>
+      <c r="B15" s="125"/>
+      <c r="C15" s="126"/>
+      <c r="D15" s="121"/>
+      <c r="E15" s="121"/>
       <c r="F15" s="78"/>
     </row>
     <row r="16" spans="1:15" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="79"/>
-      <c r="B16" s="125"/>
-      <c r="C16" s="126"/>
-      <c r="D16" s="123"/>
-      <c r="E16" s="123"/>
+      <c r="B16" s="119"/>
+      <c r="C16" s="120"/>
+      <c r="D16" s="121"/>
+      <c r="E16" s="121"/>
       <c r="F16" s="78"/>
     </row>
     <row r="17" spans="1:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="127" t="s">
+      <c r="A17" s="122" t="s">
         <v>77</v>
       </c>
-      <c r="B17" s="128"/>
-      <c r="C17" s="128"/>
-      <c r="D17" s="128"/>
-      <c r="E17" s="129"/>
+      <c r="B17" s="123"/>
+      <c r="C17" s="123"/>
+      <c r="D17" s="123"/>
+      <c r="E17" s="124"/>
       <c r="F17" s="77">
         <f>SUM(F10:F16)</f>
         <v>200</v>
@@ -12750,6 +12750,16 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="G10:O10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="A17:E17"/>
@@ -12759,16 +12769,6 @@
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="D16:E16"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="G10:O10"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D7 D18" xr:uid="{517DF1E8-3052-48CF-9AE1-C19E6ECB6686}">
@@ -13744,21 +13744,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AD10A028B4ACBB47B37340D8D4079B36" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="436e80374471046821afb96e56969fce">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="606bf0c3-7c02-4ad1-9a2b-bad21eeec9a2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="819cb4b524acab89028d2f2d821df341" ns2:_="">
     <xsd:import namespace="606bf0c3-7c02-4ad1-9a2b-bad21eeec9a2"/>
@@ -13896,39 +13881,31 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36C52544-F36B-4E63-99B1-9CCEE39BA8F0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9DD1CCA6-68F6-4337-A756-5A47702EE518}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20C1D12F-5042-471F-B3E0-E6662C5EE164}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20C1D12F-5042-471F-B3E0-E6662C5EE164}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9DD1CCA6-68F6-4337-A756-5A47702EE518}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="606bf0c3-7c02-4ad1-9a2b-bad21eeec9a2"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36C52544-F36B-4E63-99B1-9CCEE39BA8F0}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
